--- a/data/positions/Posição Consolidada - 9445242.xlsx
+++ b/data/positions/Posição Consolidada - 9445242.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 9445242 | 21/08/2026, 14:52</x:t>
+    <x:t>Conta: 9445242 | 25/08/2026, 19:24</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>100,0%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.709.029,55</x:t>
+    <x:t>R$ 1.710.619,11</x:t>
   </x:si>
   <x:si>
     <x:t>99,90%|Pós-Fixada</x:t>
@@ -88,10 +88,10 @@
     <x:t>R$ 203.561,12</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 204.129,64</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 204.001,72</x:t>
+    <x:t>R$ 204.319,50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 204.148,86</x:t>
   </x:si>
   <x:si>
     <x:t>18/08/2026</x:t>
@@ -106,10 +106,10 @@
     <x:t>R$ 1.502.802,80</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.504.899,91</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.504.428,06</x:t>
+    <x:t>R$ 1.506.299,61</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.505.512,83</x:t>
   </x:si>
   <x:si>
     <x:t>0,01%|Saldo projetado</x:t>
@@ -753,10 +753,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>1709189.68085054</x:v>
+        <x:v>1710779.24182091</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>1709029.55085054</x:v>
+        <x:v>1710619.11182091</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>160.13</x:v>

--- a/data/positions/Posição Consolidada - 9445242.xlsx
+++ b/data/positions/Posição Consolidada - 9445242.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 9445242 | 25/08/2026, 19:24</x:t>
+    <x:t>Conta: 9445242 | 28/08/2026, 09:34</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>100,0%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.710.619,11</x:t>
+    <x:t>R$ 1.713.006,23</x:t>
   </x:si>
   <x:si>
     <x:t>99,90%|Pós-Fixada</x:t>
@@ -88,10 +88,10 @@
     <x:t>R$ 203.561,12</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 204.319,50</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 204.148,86</x:t>
+    <x:t>R$ 204.604,62</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 204.369,83</x:t>
   </x:si>
   <x:si>
     <x:t>18/08/2026</x:t>
@@ -106,10 +106,10 @@
     <x:t>R$ 1.502.802,80</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.506.299,61</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.505.512,83</x:t>
+    <x:t>R$ 1.508.401,61</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.507.141,88</x:t>
   </x:si>
   <x:si>
     <x:t>0,01%|Saldo projetado</x:t>
@@ -753,10 +753,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>1710779.24182091</x:v>
+        <x:v>1713166.35853673</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>1710619.11182091</x:v>
+        <x:v>1713006.22853673</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>160.13</x:v>

--- a/data/positions/Posição Consolidada - 9445242.xlsx
+++ b/data/positions/Posição Consolidada - 9445242.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 9445242 | 28/08/2026, 09:34</x:t>
+    <x:t>Conta: 9445242 | 31/08/2026, 17:49</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>100,0%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.713.006,23</x:t>
+    <x:t>R$ 3.714.732,55</x:t>
   </x:si>
   <x:si>
     <x:t>99,90%|Pós-Fixada</x:t>
@@ -88,10 +88,10 @@
     <x:t>R$ 203.561,12</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 204.604,62</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 204.369,83</x:t>
+    <x:t>R$ 204.699,75</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 204.443,56</x:t>
   </x:si>
   <x:si>
     <x:t>18/08/2026</x:t>
@@ -106,13 +106,28 @@
     <x:t>R$ 1.502.802,80</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.508.401,61</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.507.141,88</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,01%|Saldo projetado</x:t>
+    <x:t>R$ 1.509.102,92</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.507.685,39</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.377,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.000.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.000.929,88</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.000.720,66</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 160,13</x:t>
@@ -693,7 +708,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K16"/>
+  <x:dimension ref="A1:K17"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18.139196" style="0" customWidth="1"/>
@@ -753,10 +768,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>1713166.35853673</x:v>
+        <x:v>3714892.68064607</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>1713006.22853673</x:v>
+        <x:v>3714732.55064607</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>160.13</x:v>
@@ -891,145 +906,174 @@
       <x:c r="K10" s="3"/>
     </x:row>
     <x:row r="11" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A11" s="13"/>
-      <x:c r="B11" s="13" t="s">
+      <x:c r="A11" s="12"/>
+      <x:c r="B11" s="12" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C11" s="13"/>
-      <x:c r="D11" s="13" t="s">
+      <x:c r="C11" s="12"/>
+      <x:c r="D11" s="12" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="E11" s="13" t="s">
+      <x:c r="E11" s="12" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F11" s="13" t="s">
+      <x:c r="F11" s="12" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G11" s="13" t="s">
+      <x:c r="G11" s="12" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H11" s="13" t="s">
+      <x:c r="H11" s="12" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="I11" s="13" t="s">
+      <x:c r="I11" s="12" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="J11" s="13" t="s">
+      <x:c r="J11" s="12" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="K11" s="3"/>
     </x:row>
-    <x:row r="12" spans="1:11">
-      <x:c r="A12" s="4"/>
-      <x:c r="B12" s="4"/>
-      <x:c r="C12" s="4"/>
-      <x:c r="D12" s="4"/>
-      <x:c r="E12" s="4"/>
-      <x:c r="F12" s="4"/>
-      <x:c r="G12" s="4"/>
-      <x:c r="H12" s="4"/>
-      <x:c r="I12" s="4"/>
-      <x:c r="J12" s="4"/>
-      <x:c r="K12" s="4"/>
-    </x:row>
-    <x:row r="13" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A13" s="8" t="s">
+    <x:row r="12" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A12" s="13"/>
+      <x:c r="B12" s="13" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B13" s="9"/>
-      <x:c r="C13" s="9"/>
-      <x:c r="D13" s="9"/>
-      <x:c r="E13" s="9"/>
-      <x:c r="F13" s="9"/>
-      <x:c r="G13" s="9"/>
-      <x:c r="H13" s="9"/>
-      <x:c r="I13" s="9"/>
-      <x:c r="J13" s="9"/>
-      <x:c r="K13" s="10" t="s">
+      <x:c r="C12" s="13"/>
+      <x:c r="D12" s="13" t="s">
         <x:v>33</x:v>
       </x:c>
-    </x:row>
-    <x:row r="14" spans="1:11">
-      <x:c r="A14" s="4"/>
-      <x:c r="B14" s="4"/>
-      <x:c r="C14" s="4"/>
-      <x:c r="D14" s="4"/>
-      <x:c r="E14" s="4"/>
-      <x:c r="F14" s="4"/>
-      <x:c r="G14" s="4"/>
-      <x:c r="H14" s="4"/>
-      <x:c r="I14" s="4"/>
-      <x:c r="J14" s="4"/>
-      <x:c r="K14" s="4"/>
-    </x:row>
-    <x:row r="15" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A15" s="11" t="s">
+      <x:c r="E12" s="13" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F12" s="13" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G12" s="13" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H12" s="13" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="I12" s="13" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="J12" s="13" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K12" s="3"/>
+    </x:row>
+    <x:row r="13" spans="1:11">
+      <x:c r="A13" s="4"/>
+      <x:c r="B13" s="4"/>
+      <x:c r="C13" s="4"/>
+      <x:c r="D13" s="4"/>
+      <x:c r="E13" s="4"/>
+      <x:c r="F13" s="4"/>
+      <x:c r="G13" s="4"/>
+      <x:c r="H13" s="4"/>
+      <x:c r="I13" s="4"/>
+      <x:c r="J13" s="4"/>
+      <x:c r="K13" s="4"/>
+    </x:row>
+    <x:row r="14" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A14" s="8" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B14" s="9"/>
+      <x:c r="C14" s="9"/>
+      <x:c r="D14" s="9"/>
+      <x:c r="E14" s="9"/>
+      <x:c r="F14" s="9"/>
+      <x:c r="G14" s="9"/>
+      <x:c r="H14" s="9"/>
+      <x:c r="I14" s="9"/>
+      <x:c r="J14" s="9"/>
+      <x:c r="K14" s="10" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:11">
+      <x:c r="A15" s="4"/>
+      <x:c r="B15" s="4"/>
+      <x:c r="C15" s="4"/>
+      <x:c r="D15" s="4"/>
+      <x:c r="E15" s="4"/>
+      <x:c r="F15" s="4"/>
+      <x:c r="G15" s="4"/>
+      <x:c r="H15" s="4"/>
+      <x:c r="I15" s="4"/>
+      <x:c r="J15" s="4"/>
+      <x:c r="K15" s="4"/>
+    </x:row>
+    <x:row r="16" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A16" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B15" s="11" t="s">
+      <x:c r="B16" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C15" s="11" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="D15" s="11" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E15" s="11" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F15" s="11" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="G15" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="H15" s="11" t="s">
+      <x:c r="C16" s="11" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="I15" s="11" t="s">
+      <x:c r="D16" s="11" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="J15" s="11" t="s">
+      <x:c r="E16" s="11" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="K15" s="11" t="s">
+      <x:c r="F16" s="11" t="s">
         <x:v>42</x:v>
       </x:c>
-    </x:row>
-    <x:row r="16" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A16" s="13" t="s">
+      <x:c r="G16" s="11" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B16" s="13" t="s">
+      <x:c r="H16" s="11" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C16" s="13" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D16" s="13" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E16" s="13" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F16" s="13" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="G16" s="13" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="H16" s="13" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="I16" s="13" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="J16" s="13" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="K16" s="13" t="s">
-        <x:v>44</x:v>
+      <x:c r="I16" s="11" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="J16" s="11" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="K16" s="11" t="s">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A17" s="13" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B17" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C17" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D17" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E17" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F17" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G17" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H17" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="I17" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="J17" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K17" s="13" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1037,7 +1081,7 @@
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
-    <x:mergeCell ref="A13:J13"/>
+    <x:mergeCell ref="A14:J14"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 9445242.xlsx
+++ b/data/positions/Posição Consolidada - 9445242.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 9445242 | 31/08/2026, 17:49</x:t>
+    <x:t>Conta: 9445242 | 01/09/2026, 15:59</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>100,0%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 3.714.732,55</x:t>
+    <x:t>R$ 3.716.459,68</x:t>
   </x:si>
   <x:si>
     <x:t>99,90%|Pós-Fixada</x:t>
@@ -88,10 +88,10 @@
     <x:t>R$ 203.561,12</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 204.699,75</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 204.443,56</x:t>
+    <x:t>R$ 204.794,92</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 204.517,31</x:t>
   </x:si>
   <x:si>
     <x:t>18/08/2026</x:t>
@@ -106,10 +106,10 @@
     <x:t>R$ 1.502.802,80</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.509.102,92</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.507.685,39</x:t>
+    <x:t>R$ 1.509.804,56</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.508.229,16</x:t>
   </x:si>
   <x:si>
     <x:t>28/08/2026</x:t>
@@ -124,10 +124,10 @@
     <x:t>R$ 2.000.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.000.929,88</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.000.720,66</x:t>
+    <x:t>R$ 2.001.860,19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.001.441,65</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 160,13</x:t>
@@ -768,10 +768,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>3714892.68064607</x:v>
+        <x:v>3716619.80646278</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>3714732.55064607</x:v>
+        <x:v>3716459.67646278</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>160.13</x:v>

--- a/data/positions/Posição Consolidada - 9445242.xlsx
+++ b/data/positions/Posição Consolidada - 9445242.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 9445242 | 01/09/2026, 15:59</x:t>
+    <x:t>Conta: 9445242 | 04/09/2026, 14:17</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>100,0%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 3.716.459,68</x:t>
+    <x:t>R$ 2.018.659,41</x:t>
   </x:si>
   <x:si>
     <x:t>99,90%|Pós-Fixada</x:t>
@@ -70,46 +70,28 @@
     <x:t>Valor líquido</x:t>
   </x:si>
   <x:si>
-    <x:t>13/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14/09/2026</x:t>
+    <x:t>18/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21/09/2026</x:t>
   </x:si>
   <x:si>
     <x:t>90,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>141,00</x:t>
+    <x:t>8.189,00</x:t>
   </x:si>
   <x:si>
     <x:t>0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 203.561,12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 204.794,92</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 204.517,31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>884.001,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.502.802,80</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.509.804,56</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.508.229,16</x:t>
+    <x:t>R$ 13.921,31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 14.005,69</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 13.986,70</x:t>
   </x:si>
   <x:si>
     <x:t>28/08/2026</x:t>
@@ -124,13 +106,16 @@
     <x:t>R$ 2.000.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.001.860,19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.001.441,65</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 160,13</x:t>
+    <x:t>R$ 2.004.653,72</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.003.606,63</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,01%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 160,88</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -160,7 +145,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>160,13</x:t>
+    <x:t>160,88</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -708,7 +693,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K17"/>
+  <x:dimension ref="A1:K16"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18.139196" style="0" customWidth="1"/>
@@ -768,13 +753,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>3716619.80646278</x:v>
+        <x:v>2018820.29308157</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>3716459.67646278</x:v>
+        <x:v>2018659.41308157</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>160.13</x:v>
+        <x:v>160.88</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -906,174 +891,145 @@
       <x:c r="K10" s="3"/>
     </x:row>
     <x:row r="11" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A11" s="12"/>
-      <x:c r="B11" s="12" t="s">
+      <x:c r="A11" s="13"/>
+      <x:c r="B11" s="13" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C11" s="12"/>
-      <x:c r="D11" s="12" t="s">
+      <x:c r="C11" s="13"/>
+      <x:c r="D11" s="13" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="E11" s="12" t="s">
+      <x:c r="E11" s="13" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F11" s="12" t="s">
+      <x:c r="F11" s="13" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G11" s="12" t="s">
+      <x:c r="G11" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H11" s="12" t="s">
+      <x:c r="H11" s="13" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="I11" s="12" t="s">
+      <x:c r="I11" s="13" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="J11" s="12" t="s">
+      <x:c r="J11" s="13" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="K11" s="3"/>
     </x:row>
-    <x:row r="12" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A12" s="13"/>
-      <x:c r="B12" s="13" t="s">
+    <x:row r="12" spans="1:11">
+      <x:c r="A12" s="4"/>
+      <x:c r="B12" s="4"/>
+      <x:c r="C12" s="4"/>
+      <x:c r="D12" s="4"/>
+      <x:c r="E12" s="4"/>
+      <x:c r="F12" s="4"/>
+      <x:c r="G12" s="4"/>
+      <x:c r="H12" s="4"/>
+      <x:c r="I12" s="4"/>
+      <x:c r="J12" s="4"/>
+      <x:c r="K12" s="4"/>
+    </x:row>
+    <x:row r="13" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A13" s="8" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C12" s="13"/>
-      <x:c r="D12" s="13" t="s">
+      <x:c r="B13" s="9"/>
+      <x:c r="C13" s="9"/>
+      <x:c r="D13" s="9"/>
+      <x:c r="E13" s="9"/>
+      <x:c r="F13" s="9"/>
+      <x:c r="G13" s="9"/>
+      <x:c r="H13" s="9"/>
+      <x:c r="I13" s="9"/>
+      <x:c r="J13" s="9"/>
+      <x:c r="K13" s="10" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="E12" s="13" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F12" s="13" t="s">
+    </x:row>
+    <x:row r="14" spans="1:11">
+      <x:c r="A14" s="4"/>
+      <x:c r="B14" s="4"/>
+      <x:c r="C14" s="4"/>
+      <x:c r="D14" s="4"/>
+      <x:c r="E14" s="4"/>
+      <x:c r="F14" s="4"/>
+      <x:c r="G14" s="4"/>
+      <x:c r="H14" s="4"/>
+      <x:c r="I14" s="4"/>
+      <x:c r="J14" s="4"/>
+      <x:c r="K14" s="4"/>
+    </x:row>
+    <x:row r="15" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A15" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B15" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C15" s="11" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="G12" s="13" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H12" s="13" t="s">
+      <x:c r="D15" s="11" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="I12" s="13" t="s">
+      <x:c r="E15" s="11" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="J12" s="13" t="s">
+      <x:c r="F15" s="11" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="K12" s="3"/>
-    </x:row>
-    <x:row r="13" spans="1:11">
-      <x:c r="A13" s="4"/>
-      <x:c r="B13" s="4"/>
-      <x:c r="C13" s="4"/>
-      <x:c r="D13" s="4"/>
-      <x:c r="E13" s="4"/>
-      <x:c r="F13" s="4"/>
-      <x:c r="G13" s="4"/>
-      <x:c r="H13" s="4"/>
-      <x:c r="I13" s="4"/>
-      <x:c r="J13" s="4"/>
-      <x:c r="K13" s="4"/>
-    </x:row>
-    <x:row r="14" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A14" s="8" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B14" s="9"/>
-      <x:c r="C14" s="9"/>
-      <x:c r="D14" s="9"/>
-      <x:c r="E14" s="9"/>
-      <x:c r="F14" s="9"/>
-      <x:c r="G14" s="9"/>
-      <x:c r="H14" s="9"/>
-      <x:c r="I14" s="9"/>
-      <x:c r="J14" s="9"/>
-      <x:c r="K14" s="10" t="s">
+      <x:c r="G15" s="11" t="s">
         <x:v>38</x:v>
       </x:c>
-    </x:row>
-    <x:row r="15" spans="1:11">
-      <x:c r="A15" s="4"/>
-      <x:c r="B15" s="4"/>
-      <x:c r="C15" s="4"/>
-      <x:c r="D15" s="4"/>
-      <x:c r="E15" s="4"/>
-      <x:c r="F15" s="4"/>
-      <x:c r="G15" s="4"/>
-      <x:c r="H15" s="4"/>
-      <x:c r="I15" s="4"/>
-      <x:c r="J15" s="4"/>
-      <x:c r="K15" s="4"/>
-    </x:row>
-    <x:row r="16" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A16" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B16" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C16" s="11" t="s">
+      <x:c r="H15" s="11" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D16" s="11" t="s">
+      <x:c r="I15" s="11" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E16" s="11" t="s">
+      <x:c r="J15" s="11" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F16" s="11" t="s">
+      <x:c r="K15" s="11" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="G16" s="11" t="s">
+    </x:row>
+    <x:row r="16" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A16" s="13" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="H16" s="11" t="s">
+      <x:c r="B16" s="13" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="I16" s="11" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="J16" s="11" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="K16" s="11" t="s">
-        <x:v>47</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A17" s="13" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B17" s="13" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C17" s="13" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D17" s="13" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E17" s="13" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F17" s="13" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="G17" s="13" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="H17" s="13" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="I17" s="13" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="J17" s="13" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="K17" s="13" t="s">
-        <x:v>49</x:v>
+      <x:c r="C16" s="13" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D16" s="13" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E16" s="13" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F16" s="13" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G16" s="13" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H16" s="13" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="I16" s="13" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="J16" s="13" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="K16" s="13" t="s">
+        <x:v>44</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1081,7 +1037,7 @@
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
-    <x:mergeCell ref="A14:J14"/>
+    <x:mergeCell ref="A13:J13"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 9445242.xlsx
+++ b/data/positions/Posição Consolidada - 9445242.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 9445242 | 04/09/2026, 14:17</x:t>
+    <x:t>Conta: 9445242 | 10/09/2026, 14:06</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>100,0%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.018.659,41</x:t>
+    <x:t>R$ 1.520.531,27</x:t>
   </x:si>
   <x:si>
     <x:t>99,90%|Pós-Fixada</x:t>
@@ -70,52 +70,31 @@
     <x:t>Valor líquido</x:t>
   </x:si>
   <x:si>
-    <x:t>18/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21/09/2026</x:t>
+    <x:t>28/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29/09/2026</x:t>
   </x:si>
   <x:si>
     <x:t>90,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>8.189,00</x:t>
+    <x:t>1.043,00</x:t>
   </x:si>
   <x:si>
     <x:t>0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 13.921,31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 14.005,69</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 13.986,70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.377,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.000.000,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.004.653,72</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.003.606,63</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,01%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 160,88</x:t>
+    <x:t>R$ 1.514.887,44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.519.261,41</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,02%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 315,21</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -145,7 +124,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>160,88</x:t>
+    <x:t>315,21</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -341,7 +320,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="14">
+  <x:cellXfs count="13">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -387,10 +366,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -693,7 +668,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K16"/>
+  <x:dimension ref="A1:K15"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18.139196" style="0" customWidth="1"/>
@@ -753,13 +728,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>2018820.29308157</x:v>
+        <x:v>1520846.476968</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>2018659.41308157</x:v>
+        <x:v>1520531.266968</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>160.88</x:v>
+        <x:v>315.21</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -883,153 +858,124 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="J10" s="12" t="s">
+      <x:c r="K10" s="3"/>
+    </x:row>
+    <x:row r="11" spans="1:11">
+      <x:c r="A11" s="4"/>
+      <x:c r="B11" s="4"/>
+      <x:c r="C11" s="4"/>
+      <x:c r="D11" s="4"/>
+      <x:c r="E11" s="4"/>
+      <x:c r="F11" s="4"/>
+      <x:c r="G11" s="4"/>
+      <x:c r="H11" s="4"/>
+      <x:c r="I11" s="4"/>
+      <x:c r="J11" s="4"/>
+      <x:c r="K11" s="4"/>
+    </x:row>
+    <x:row r="12" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A12" s="8" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="K10" s="3"/>
-    </x:row>
-    <x:row r="11" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A11" s="13"/>
-      <x:c r="B11" s="13" t="s">
+      <x:c r="B12" s="9"/>
+      <x:c r="C12" s="9"/>
+      <x:c r="D12" s="9"/>
+      <x:c r="E12" s="9"/>
+      <x:c r="F12" s="9"/>
+      <x:c r="G12" s="9"/>
+      <x:c r="H12" s="9"/>
+      <x:c r="I12" s="9"/>
+      <x:c r="J12" s="9"/>
+      <x:c r="K12" s="10" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C11" s="13"/>
-      <x:c r="D11" s="13" t="s">
+    </x:row>
+    <x:row r="13" spans="1:11">
+      <x:c r="A13" s="4"/>
+      <x:c r="B13" s="4"/>
+      <x:c r="C13" s="4"/>
+      <x:c r="D13" s="4"/>
+      <x:c r="E13" s="4"/>
+      <x:c r="F13" s="4"/>
+      <x:c r="G13" s="4"/>
+      <x:c r="H13" s="4"/>
+      <x:c r="I13" s="4"/>
+      <x:c r="J13" s="4"/>
+      <x:c r="K13" s="4"/>
+    </x:row>
+    <x:row r="14" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A14" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B14" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="E11" s="13" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F11" s="13" t="s">
+      <x:c r="D14" s="11" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G11" s="13" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H11" s="13" t="s">
+      <x:c r="E14" s="11" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="I11" s="13" t="s">
+      <x:c r="F14" s="11" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="J11" s="13" t="s">
+      <x:c r="G14" s="11" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="K11" s="3"/>
-    </x:row>
-    <x:row r="12" spans="1:11">
-      <x:c r="A12" s="4"/>
-      <x:c r="B12" s="4"/>
-      <x:c r="C12" s="4"/>
-      <x:c r="D12" s="4"/>
-      <x:c r="E12" s="4"/>
-      <x:c r="F12" s="4"/>
-      <x:c r="G12" s="4"/>
-      <x:c r="H12" s="4"/>
-      <x:c r="I12" s="4"/>
-      <x:c r="J12" s="4"/>
-      <x:c r="K12" s="4"/>
-    </x:row>
-    <x:row r="13" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A13" s="8" t="s">
+      <x:c r="H14" s="11" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B13" s="9"/>
-      <x:c r="C13" s="9"/>
-      <x:c r="D13" s="9"/>
-      <x:c r="E13" s="9"/>
-      <x:c r="F13" s="9"/>
-      <x:c r="G13" s="9"/>
-      <x:c r="H13" s="9"/>
-      <x:c r="I13" s="9"/>
-      <x:c r="J13" s="9"/>
-      <x:c r="K13" s="10" t="s">
+      <x:c r="I14" s="11" t="s">
         <x:v>33</x:v>
       </x:c>
-    </x:row>
-    <x:row r="14" spans="1:11">
-      <x:c r="A14" s="4"/>
-      <x:c r="B14" s="4"/>
-      <x:c r="C14" s="4"/>
-      <x:c r="D14" s="4"/>
-      <x:c r="E14" s="4"/>
-      <x:c r="F14" s="4"/>
-      <x:c r="G14" s="4"/>
-      <x:c r="H14" s="4"/>
-      <x:c r="I14" s="4"/>
-      <x:c r="J14" s="4"/>
-      <x:c r="K14" s="4"/>
-    </x:row>
-    <x:row r="15" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A15" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B15" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C15" s="11" t="s">
+      <x:c r="J14" s="11" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="D15" s="11" t="s">
+      <x:c r="K14" s="11" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="E15" s="11" t="s">
+    </x:row>
+    <x:row r="15" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A15" s="12" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="F15" s="11" t="s">
+      <x:c r="B15" s="12" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="G15" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="H15" s="11" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="I15" s="11" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="J15" s="11" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="K15" s="11" t="s">
-        <x:v>42</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A16" s="13" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B16" s="13" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C16" s="13" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D16" s="13" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E16" s="13" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F16" s="13" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="G16" s="13" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="H16" s="13" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="I16" s="13" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="J16" s="13" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="K16" s="13" t="s">
-        <x:v>44</x:v>
+      <x:c r="C15" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D15" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E15" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F15" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G15" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H15" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="I15" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="J15" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K15" s="12" t="s">
+        <x:v>37</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1037,7 +983,7 @@
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
-    <x:mergeCell ref="A13:J13"/>
+    <x:mergeCell ref="A12:J12"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 9445242.xlsx
+++ b/data/positions/Posição Consolidada - 9445242.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 9445242 | 10/09/2026, 14:06</x:t>
+    <x:t>Conta: 9445242 | 16/09/2026, 08:43</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,69 +34,15 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>100,0%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.520.531,27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>99,90%|Pós-Fixada</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Aplicação</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Carência</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Vencimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Taxa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Disponível</x:t>
+    <x:t>100%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 628,73</x:t>
   </x:si>
   <x:si>
     <x:t>Garantia</x:t>
   </x:si>
   <x:si>
-    <x:t>Valor aplicado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Posição</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Valor líquido</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>90,00% CDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.043,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.514.887,44</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.519.261,41</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,02%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 315,21</x:t>
-  </x:si>
-  <x:si>
     <x:t>Resgate de fundo pendente</x:t>
   </x:si>
   <x:si>
@@ -124,7 +70,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>315,21</x:t>
+    <x:t>628,73</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -668,7 +614,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K15"/>
+  <x:dimension ref="A1:K10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18.139196" style="0" customWidth="1"/>
@@ -728,13 +674,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>1520846.476968</x:v>
+        <x:v>628.73</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>1520531.266968</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>315.21</x:v>
+        <x:v>628.73</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -782,13 +728,13 @@
       <x:c r="D7" s="9"/>
       <x:c r="E7" s="9"/>
       <x:c r="F7" s="9"/>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="9"/>
+      <x:c r="H7" s="9"/>
+      <x:c r="I7" s="9"/>
+      <x:c r="J7" s="9"/>
+      <x:c r="K7" s="10" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="3"/>
-      <x:c r="I7" s="3"/>
-      <x:c r="J7" s="3"/>
-      <x:c r="K7" s="3"/>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="4"/>
@@ -798,192 +744,86 @@
       <x:c r="E8" s="4"/>
       <x:c r="F8" s="4"/>
       <x:c r="G8" s="4"/>
-      <x:c r="H8" s="3"/>
-      <x:c r="I8" s="3"/>
-      <x:c r="J8" s="3"/>
-      <x:c r="K8" s="3"/>
+      <x:c r="H8" s="4"/>
+      <x:c r="I8" s="4"/>
+      <x:c r="J8" s="4"/>
+      <x:c r="K8" s="4"/>
     </x:row>
     <x:row r="9" spans="1:11" ht="35.1" customHeight="1">
       <x:c r="A9" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B9" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B9" s="11" t="s">
+      <x:c r="C9" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="D9" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="E9" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="F9" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="G9" s="11" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="H9" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="H9" s="11" t="s">
+      <x:c r="I9" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="I9" s="11" t="s">
+      <x:c r="J9" s="11" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="s">
+      <x:c r="K9" s="11" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="K9" s="3"/>
     </x:row>
     <x:row r="10" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A10" s="12"/>
+      <x:c r="A10" s="12" t="s">
+        <x:v>18</x:v>
+      </x:c>
       <x:c r="B10" s="12" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C10" s="12"/>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C10" s="12" t="s">
+        <x:v>19</x:v>
+      </x:c>
       <x:c r="D10" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="E10" s="12" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F10" s="12" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G10" s="12" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H10" s="12" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J10" s="12" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K10" s="3"/>
-    </x:row>
-    <x:row r="11" spans="1:11">
-      <x:c r="A11" s="4"/>
-      <x:c r="B11" s="4"/>
-      <x:c r="C11" s="4"/>
-      <x:c r="D11" s="4"/>
-      <x:c r="E11" s="4"/>
-      <x:c r="F11" s="4"/>
-      <x:c r="G11" s="4"/>
-      <x:c r="H11" s="4"/>
-      <x:c r="I11" s="4"/>
-      <x:c r="J11" s="4"/>
-      <x:c r="K11" s="4"/>
-    </x:row>
-    <x:row r="12" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A12" s="8" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B12" s="9"/>
-      <x:c r="C12" s="9"/>
-      <x:c r="D12" s="9"/>
-      <x:c r="E12" s="9"/>
-      <x:c r="F12" s="9"/>
-      <x:c r="G12" s="9"/>
-      <x:c r="H12" s="9"/>
-      <x:c r="I12" s="9"/>
-      <x:c r="J12" s="9"/>
-      <x:c r="K12" s="10" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:11">
-      <x:c r="A13" s="4"/>
-      <x:c r="B13" s="4"/>
-      <x:c r="C13" s="4"/>
-      <x:c r="D13" s="4"/>
-      <x:c r="E13" s="4"/>
-      <x:c r="F13" s="4"/>
-      <x:c r="G13" s="4"/>
-      <x:c r="H13" s="4"/>
-      <x:c r="I13" s="4"/>
-      <x:c r="J13" s="4"/>
-      <x:c r="K13" s="4"/>
-    </x:row>
-    <x:row r="14" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A14" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B14" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C14" s="11" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D14" s="11" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E14" s="11" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F14" s="11" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G14" s="11" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="H14" s="11" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="I14" s="11" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="J14" s="11" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="K14" s="11" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A15" s="12" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="F15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="G15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="H15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="I15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="J15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="K15" s="12" t="s">
-        <x:v>37</x:v>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="K10" s="12" t="s">
+        <x:v>19</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="4">
+  <x:mergeCells count="3">
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
-    <x:mergeCell ref="A7:F7"/>
-    <x:mergeCell ref="A12:J12"/>
+    <x:mergeCell ref="A7:J7"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 9445242.xlsx
+++ b/data/positions/Posição Consolidada - 9445242.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 9445242 | 16/09/2026, 08:43</x:t>
+    <x:t>Conta: 9445242 | 21/09/2026, 16:40</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 9445242.xlsx
+++ b/data/positions/Posição Consolidada - 9445242.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 9445242 | 21/09/2026, 16:40</x:t>
+    <x:t>Conta: 9445242 | 23/09/2026, 09:37</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 9445242.xlsx
+++ b/data/positions/Posição Consolidada - 9445242.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 9445242 | 23/09/2026, 09:37</x:t>
+    <x:t>Conta: 9445242 | 30/09/2026, 08:52</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 9445242.xlsx
+++ b/data/positions/Posição Consolidada - 9445242.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 9445242 | 30/09/2026, 08:52</x:t>
+    <x:t>Conta: 9445242 | 13/10/2026, 11:10</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>100%|Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 628,73</x:t>
+    <x:t>R$ 368,58</x:t>
   </x:si>
   <x:si>
     <x:t>Garantia</x:t>
@@ -70,7 +70,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>628,73</x:t>
+    <x:t>368,58</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -674,13 +674,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>628.73</x:v>
+        <x:v>368.58</x:v>
       </x:c>
       <x:c r="B4" s="7">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>628.73</x:v>
+        <x:v>368.58</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>

--- a/data/positions/Posição Consolidada - 9445242.xlsx
+++ b/data/positions/Posição Consolidada - 9445242.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 9445242 | 13/10/2026, 11:10</x:t>
+    <x:t>Conta: 9445242 | 14/10/2026, 08:49</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>100%|Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 368,58</x:t>
+    <x:t>R$ 707,85</x:t>
   </x:si>
   <x:si>
     <x:t>Garantia</x:t>
@@ -74,6 +74,9 @@
   </x:si>
   <x:si>
     <x:t>0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>339,27</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -674,7 +677,7 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>368.58</x:v>
+        <x:v>707.85</x:v>
       </x:c>
       <x:c r="B4" s="7">
         <x:v>0</x:v>
@@ -683,7 +686,7 @@
         <x:v>368.58</x:v>
       </x:c>
       <x:c r="D4" s="7">
-        <x:v>0</x:v>
+        <x:v>339.27</x:v>
       </x:c>
       <x:c r="E4" s="4"/>
       <x:c r="F4" s="4"/>
@@ -804,10 +807,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="G10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
         <x:v>19</x:v>

--- a/data/positions/Posição Consolidada - 9445242.xlsx
+++ b/data/positions/Posição Consolidada - 9445242.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 9445242 | 14/10/2026, 08:49</x:t>
+    <x:t>Conta: 9445242 | 27/10/2026, 19:01</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -70,13 +70,10 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>368,58</x:t>
+    <x:t>707,85</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>339,27</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -683,10 +680,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>368.58</x:v>
+        <x:v>707.85</x:v>
       </x:c>
       <x:c r="D4" s="7">
-        <x:v>339.27</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E4" s="4"/>
       <x:c r="F4" s="4"/>
@@ -807,10 +804,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="G10" s="12" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H10" s="12" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
         <x:v>19</x:v>

--- a/data/positions/Posição Consolidada - 9445242.xlsx
+++ b/data/positions/Posição Consolidada - 9445242.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 9445242 | 27/10/2026, 19:01</x:t>
+    <x:t>Conta: 9445242 | 29/10/2026, 16:12</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
